--- a/trading_history.xlsx
+++ b/trading_history.xlsx
@@ -37,7 +37,7 @@
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -56,8 +56,12 @@
       <b val="1"/>
       <color rgb="009C0006"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00006100"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -82,6 +86,12 @@
         <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -95,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -104,6 +114,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -469,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE18"/>
+  <dimension ref="A1:AE62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2328,7 +2339,7 @@
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>46010.68734708648</v>
+        <v>46010.68734708333</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2429,13 +2440,4589 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr"/>
-      <c r="AB18" t="inlineStr"/>
-      <c r="AC18" t="inlineStr"/>
-      <c r="AD18" t="inlineStr"/>
-      <c r="AE18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>46017.62105354167</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Boom 1000 Index</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>BOOM → Solo señales de COMPRA permitidas</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>50.17</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>333</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>La regresión Macro en H1 está apuntando al alcista, pero el MACD, Heikin Ashi y EMA Strategy están indicando una tendencia neutral o baja. La regla de confluencia no se cumple actualmente.</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>46017.62122267361</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Boom 500 Index</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>BOOM → Solo señales de COMPRA permitidas</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>628</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>La regresión tiene un R2 de 75.8% en sentido alcista, pero el MACD está en bajada y la EMA Strategy muestra venta. Heikin Ashi es el único indicador que confirma una tendencia alcista.</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>46017.62141868056</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Boom 300 Index</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>BOOM → Solo señales de COMPRA permitidas</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>62.62</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>VENDER</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>333</v>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Regresión Macro (H1) presenta dirección bajista, mientras que panel técnico (M5) es neutro. Además, el RSI está sobrecompra y MACD está bajista, sin embargo, Heikin Ashi indica alcista. Por lo tanto, </t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>46017.62167224537</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Boom 600 Index</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>BOOM → Solo señales de COMPRA permitidas</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>23.28</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>45</v>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>La regresión Macro en H1 tiene una dirección bajista del 23.28% y la Panel Tecnico en M5 es neutra con un 11.1%. Aunque Heikin Ashi está verde indicando alcista, RSI está sobrecompra con un valor de 4</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>46017.62190553241</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Boom 900 Index</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>BOOM → Solo señales de COMPRA permitidas</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>333</v>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>La Regresión Macro (H1) tiene un valor del 6.49% en dirección alcista y el Panel Técnico (M5) indica un estado neutral de 33.3%, sin embargo, no hay confluencia alcista confirmada en RSI, MACD o Heiki</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U23" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>46017.62214969908</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Crash 1000 Index</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CRASH → Solo señales de VENTA permitidas</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>75</v>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>En el Crash 1000 Index, se observa una sobrecompra según el RSI (60.2), lo que sugiere que la venta puede ser una buena opción. Además, el MACD está en alzista y Heikin Ashi es bajista, lo que confirm</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>BLOQUEO: IA y Regresion en direcciones OPUESTAS.</t>
+        </is>
+      </c>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>46017.62237793981</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Crash 500 Index</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CRASH → Solo señales de VENTA permitidas</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>15.39</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>63.7</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>50</v>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>A pesar de que la regresión tiene una dirección alistista, no se observa coincidencia bajista entre los gatillos MACD y Heikin Ashi. Además, el RSI está sobrecompra (63.7) y las estrategias EMA y Stoc</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>46017.62257717593</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Crash 300 Index</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CRASH → Solo señales de VENTA permitidas</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>90.61</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>667</v>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>La Regresión Macro en H1 está mostrando una tendencia alista con un R2 de 90.61%, pero el MACD y Heikin Ashi están bajistas. Además, el RSI no muestra un sobrecompra ni sobreventa, por lo que es prude</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>46017.62279666667</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Crash 600 Index</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CRASH → Solo señales de VENTA permitidas</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>16.57</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O27" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>50</v>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>La regresión en el tiempo macro (H1) indica una dirección bajista del 16.57%, sin embargo, no hay coincidencia técnica como RSI alto, MACD cruzando bajista o Heikin Ashi rojo. Como las reglas específi</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>46017.62301471065</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Crash 900 Index</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CRASH → Solo señales de VENTA permitidas</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O28" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>50</v>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>En este momento, no hay confluencia técnica clara para emitir una señal de venta según las reglas especificadas. La Regresión Macro tiene dirección alciista (1.83%) pero se contrarresta por el indicad</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>46017.62319587963</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Jump 75 Index</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>GENÉRICO → Análisis completo</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O29" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>50</v>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>La Regresión Macro muestra dirección bajista y el RSI está en sobrecompra. Sin embargo, el Heikin Ashi indica alcista y el MACD está bajando. Debido a la discrepancia entre estos indicadores, es prude</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>46017.6233997801</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Volatility 10 Index</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>VOLATILITY → Permite COMPRA/VENTA según tendencia</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>79.79000000000001</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>64.7</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O30" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>7979</v>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>EJECUCION: Alta confianza IA (7979%) alineada con Macro.</t>
+        </is>
+      </c>
+      <c r="U30" s="6" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="V30" t="n">
+        <v>5706.93</v>
+      </c>
+      <c r="W30" t="n">
+        <v>500</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>46017.62361434028</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Volatility 100 Index</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>VOLATILITY → Permite COMPRA/VENTA según tendencia</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>72.73</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>VENDER</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O31" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>7273</v>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>La regresión lineal en H1 indica una tendencia descendente con un 72.73% de confianza, confirmada por la dirección alta del MACD y Heikin Ashi. Además, el RSI está dentro del rango neutral (54.6), y h</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>BLOQUEO: IA y Regresion en direcciones OPUESTAS.</t>
+        </is>
+      </c>
+      <c r="U31" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>46017.62389135417</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Volatility 25 Index</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>VOLATILITY → Permite COMPRA/VENTA según tendencia</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>41.58</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>VENDER</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O32" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>667</v>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>La regresión lineal en H1 presenta una tendencia bajista del 41.58%, sin embargo, el panel técnico en M5 es neutral. La RSI se encuentra en una zona de sobrecompra y la MACD, Heikin Ashi y EMA Strateg</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>46017.6241199537</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Volatility 50 Index</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>VOLATILITY → Permite COMPRA/VENTA según tendencia</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O33" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>426</v>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>La Regresión Macro presenta una dirección bajista en H1 (31.5%), mientras que el panel técnico es neutral en M5 (11.1%). El RSI se encuentra en la zona de sobrecompra, y aunque el MACD y Heikin Ashi a</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U33" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>46017.62430165509</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Volatility 75 Index</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>VOLATILITY → Permite COMPRA/VENTA según tendencia</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>72.55</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O34" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>7255</v>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>EJECUCION: Alta confianza IA (7255%) alineada con Macro.</t>
+        </is>
+      </c>
+      <c r="U34" s="6" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="V34" t="n">
+        <v>43635.81</v>
+      </c>
+      <c r="W34" t="n">
+        <v>500</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>46017.62450384259</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>XAUUSD → Permite COMPRA/VENTA (requiere alta confirmación)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>73.23999999999999</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>31</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O35" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>444</v>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>La regresión tiene dirección alistica, pero el RSI y el MACD indican una sobrecompra y bajista respectivamente. Además, las demás indicadores no confirman la tendencia. Es necesaria más confluencia pa</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>46017.62608244213</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Boom 1000 Index</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>BOOM → Solo señales de COMPRA permitidas</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>64.34</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O36" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>333</v>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>La Regresión Macro en H1 indica un estado alcista pero solo con un 33.3% de confianza, no se ha encontrado suficiente confluencia técnica (RSI bajo, MACD cruzando alcista, Heikin Ashi verde) para emit</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U36" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n">
+        <v>46017.62629886574</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Boom 500 Index</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>BOOM → Solo señales de COMPRA permitidas</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>44.35</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O37" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>333</v>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>No se ha encontrado confluencia alcista en el momento actual, RSI y MACD están bajistas y Heikin Ashi también está bajista. Además, EMA Strategy indica venta. Sin embargo, la regresión macro de H1 tie</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U37" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>46017.62647211806</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Boom 300 Index</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>BOOM → Solo señales de COMPRA permitidas</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O38" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>222</v>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Se ha identificado una tendencia neutral en el panel técnico M5 y baja dirección en la regresión Macro H1, lo que indica falta de confluencia alcista para emitir una señal de compra. Se recomienda esp</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>46017.62668939814</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Boom 600 Index</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>BOOM → Solo señales de COMPRA permitidas</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>39.55</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O39" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>75</v>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El MACD está en alcista y el RSI se encuentra por debajo de 65, lo que indica una sobrecompra posible. Sin embargo, el Heikin Ashi está en baja, lo que es un signo ligeramente contrario. Sin embargo, </t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>BLOQUEO: IA y Regresion en direcciones OPUESTAS.</t>
+        </is>
+      </c>
+      <c r="U39" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="n">
+        <v>46017.62689240741</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Boom 900 Index</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>BOOM → Solo señales de COMPRA permitidas</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>18.64</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O40" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>40</v>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>La regresión macro en H1 está indicando una dirección alista, pero los gatillos MACD y Heikin Ashi no confirmaron esa tendencia. Además, el RSI se encuentra sobrecompra con un valor de 21.5. Por lo ta</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U40" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n">
+        <v>46017.62711271991</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Crash 1000 Index</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>CRASH → Solo señales de VENTA permitidas</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>15.87</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O41" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>60</v>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>Aunque la Regresión Macro (H1) muestra un valor alto (15.87%) en sentido alistista, el RSI se encuentra sobre el 51.2% lo que indica sobrecompra. Además, el MACD está en alistista y Heikin Ashi es baj</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U41" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V41" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n">
+        <v>46017.62729516203</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Crash 500 Index</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CRASH → Solo señales de VENTA permitidas</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>71.52</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O42" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>50</v>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aunque la regresión macro (H1) muestra una alciista del 71.52%, no se confirma con el MACD, Heikin Ashi y RSI, los cuales están indicando una sobreventa, por lo tanto es mejor esperar a encontrar una </t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="n">
+        <v>46017.62754586805</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Crash 300 Index</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>CRASH → Solo señales de VENTA permitidas</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>91.79000000000001</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O43" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>9179</v>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>La regresión Macro en H1 es alcista (91.79%) indicando una tendencia de subida. Sin embargo, el RSI está sobrecompra (72.2), MACD también alcista y Heikin Ashi bajista, lo que indica una posible tende</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>BLOQUEO: IA y Regresion en direcciones OPUESTAS.</t>
+        </is>
+      </c>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="n">
+        <v>46017.62772520833</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Crash 600 Index</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>CRASH → Solo señales de VENTA permitidas</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O44" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>222</v>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>Aunque la regresión macro (H1) indica una tendencia alistista, no hay confluencia bajista entre MACD, Heikin Ashi o RSI para dar una señal de venta. En este caso, es mejor esperar a que se produzca un</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U44" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="n">
+        <v>46017.62789821759</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Crash 900 Index</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>CRASH → Solo señales de VENTA permitidas</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>60.3</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O45" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>60</v>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Con fluencia técnica actual: RSI en sobrecompra (60.3), MACD y Heikin Ashi bajistas, Regresión Macro con dirección alistista pero solo un 1.92%. No se detecta confluencia para ninguna señal de compra </t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U45" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V45" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="n">
+        <v>46017.62809283565</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Jump 75 Index</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>GENÉRICO → Análisis completo</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>83.12</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>VENDER</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O46" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>7368</v>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>BLOQUEO: IA y Regresion en direcciones OPUESTAS.</t>
+        </is>
+      </c>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="n">
+        <v>46017.62826092593</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Volatility 10 Index</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>VOLATILITY → Permite COMPRA/VENTA según tendencia</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>79.76000000000001</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O47" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>7976</v>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>La regresión lineal en el macro tiempo (H1) tiene un 79.76% de confianza en la dirección alzista, y el MACD también está confirmando esta tendencia. Además, las medias exponenciales (EMA Strategy) tam</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>EJECUCION: Alta confianza IA (7976%) alineada con Macro.</t>
+        </is>
+      </c>
+      <c r="U47" s="6" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="V47" t="n">
+        <v>5706.87</v>
+      </c>
+      <c r="W47" t="n">
+        <v>500</v>
+      </c>
+      <c r="X47" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="n">
+        <v>46017.64341837963</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Volatility 10 Index</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>VOLATILITY → Permite COMPRA/VENTA según tendencia</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>79.77</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O48" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>50</v>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>La regresión lineal en H1 tiene una alta confianza (79.77%) indicando tendencia al ciste, sin embargo, el panel técnico en M5 es neutro y la dirección de MACD y Heikin Ashi están en bajada. Además, la</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U48" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V48" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="n">
+        <v>46017.64365708333</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Volatility 10 Index</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>VOLATILITY → Permite COMPRA/VENTA según tendencia</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>79.77</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O49" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>544</v>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>La regresión lineal muestra un estado alistico (79.77%), pero la mayoría de los indicadores técnicos no están confirmando esta tendencia. El RSI y el MACD están en neutral, Heikin Ashi bajista, EMA St</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U49" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V49" t="n">
+        <v>0</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0</v>
+      </c>
+      <c r="X49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="n">
+        <v>46017.64395616898</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Volatility 10 Index</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>VOLATILITY → Permite COMPRA/VENTA según tendencia</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>79.76000000000001</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O50" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>543</v>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>Aunque la regresión lineal (H1) tiene una alta confianza alistica, se observa una tendencia neutral en el panel técnico (M5). Además, el RSI se encuentra en el nivel de sobrecompra pero no hay confirm</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U50" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V50" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0</v>
+      </c>
+      <c r="X50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="n">
+        <v>46017.64413917824</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Volatility 10 Index</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>VOLATILITY → Permite COMPRA/VENTA según tendencia</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>79.76000000000001</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>56</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O51" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>50</v>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>Regresión Macro en H1 es alcista pero Panel Técnico en M5 es neutral. RSI y MACD no actúan como gatillos de entrada, además, el volumen no se está considerando en este contexto.</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U51" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V51" t="n">
+        <v>0</v>
+      </c>
+      <c r="W51" t="n">
+        <v>0</v>
+      </c>
+      <c r="X51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="n">
+        <v>46017.64456708333</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Volatility 10 Index</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>VOLATILITY → Permite COMPRA/VENTA según tendencia</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>79.76000000000001</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O52" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>543</v>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U52" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V52" t="n">
+        <v>0</v>
+      </c>
+      <c r="W52" t="n">
+        <v>0</v>
+      </c>
+      <c r="X52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="n">
+        <v>46017.64473666667</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Volatility 10 Index</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>VOLATILITY → Permite COMPRA/VENTA según tendencia</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>79.76000000000001</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O53" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>508</v>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>La regresión lineal tiene dirección alistica, pero hay discrepancias en los indicadores MACD y Estocastico que han bajado, Heikin Ashi que es alistica, EMA Strategy que recomienda compra y Micro sopor</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U53" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V53" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" t="n">
+        <v>0</v>
+      </c>
+      <c r="X53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="n">
+        <v>46017.64510269676</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Volatility 10 Index</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>VOLATILITY → Permite COMPRA/VENTA según tendencia</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>79.76000000000001</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O54" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>5432</v>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">La regresión lineal macro en H1 muestra una tendencia al alza (79.76%), sin embargo, el panel técnico en M5 indica neutralidad (22.2%) y la MACD está bajando. Además, el RSI se encuentra dentro de la </t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U54" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V54" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" t="n">
+        <v>0</v>
+      </c>
+      <c r="X54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="n">
+        <v>46017.64528837963</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Volatility 10 Index</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>VOLATILITY → Permite COMPRA/VENTA según tendencia</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>79.76000000000001</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O55" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>573</v>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Aunque la regresión lineal está indicando alistamiento, hay una baja confianza en las tendencias técnicas como MACD, Heikin Ashi y Estocastico que no han confirmado esta dirección. Además, el RSI se e</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U55" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V55" t="n">
+        <v>0</v>
+      </c>
+      <c r="W55" t="n">
+        <v>0</v>
+      </c>
+      <c r="X55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="n">
+        <v>46017.64568946759</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Volatility 10 Index</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>VOLATILITY → Permite COMPRA/VENTA según tendencia</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>79.76000000000001</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O56" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>495</v>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>La Regresión Macro en H1 tiene un 79.76% de dirección alista, sin embargo el Panel Técnico en M5 muestra una dirección neutra y MACD esta bajando, Heikin Ashi está alista pero no es suficiente para co</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U56" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V56" t="n">
+        <v>0</v>
+      </c>
+      <c r="W56" t="n">
+        <v>0</v>
+      </c>
+      <c r="X56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="n">
+        <v>46017.64586135417</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Volatility 10 Index</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>VOLATILITY → Permite COMPRA/VENTA según tendencia</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>79.76000000000001</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O57" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>542</v>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U57" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V57" t="n">
+        <v>0</v>
+      </c>
+      <c r="W57" t="n">
+        <v>0</v>
+      </c>
+      <c r="X57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="n">
+        <v>46017.64614451389</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Volatility 10 Index</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>VOLATILITY → Permite COMPRA/VENTA según tendencia</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>79.76000000000001</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O58" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>556</v>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>La regresión lineal tiene una tendencia alista pero el panel técnico tiene dirección bajista, la señal debe esperarse para confirmar la tendencia.</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U58" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V58" t="n">
+        <v>0</v>
+      </c>
+      <c r="W58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="n">
+        <v>46017.64662210648</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Volatility 10 Index</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>VOLATILITY → Permite COMPRA/VENTA según tendencia</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>79.76000000000001</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O59" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>50</v>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>La regresión lineal se encuentra alistada, sin embargo, el MACD y el Estocastico apuntan a una venta. Es preciso esperar a que se confirme la tendencia antes de emitir una señal decisiva.</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U59" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V59" t="n">
+        <v>0</v>
+      </c>
+      <c r="W59" t="n">
+        <v>0</v>
+      </c>
+      <c r="X59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>46017.64714653936</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Volatility 10 Index</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>VOLATILITY → Permite COMPRA/VENTA según tendencia</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>79.76000000000001</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O60" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>50</v>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U60" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V60" t="n">
+        <v>0</v>
+      </c>
+      <c r="W60" t="n">
+        <v>0</v>
+      </c>
+      <c r="X60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="n">
+        <v>46017.64764547454</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Volatility 10 Index</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>VOLATILITY → Permite COMPRA/VENTA según tendencia</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>79.76000000000001</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O61" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>569</v>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>La regresión lineal tiene una dirección alistista, pero no hay confirme de ello por el MACD o Heikin Ashi. Además, la RSI se encuentra en la zona de sobrecompra. Se recomienda esperar a que se corrobo</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U61" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V61" t="n">
+        <v>0</v>
+      </c>
+      <c r="W61" t="n">
+        <v>0</v>
+      </c>
+      <c r="X61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="n">
+        <v>46017.64814373328</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Volatility 10 Index</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>VOLATILITY → Permite COMPRA/VENTA según tendencia</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>79.76000000000001</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O62" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>50</v>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">La Regresión Macro tiene dirección alcista pero el MACD y RSI no están confirmando esa dirección. Heikin Ashi también está mostrando alcista. Sin embargo, la mayoría de los indicadores no son a favor </t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U62" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W62" t="n">
+        <v>0</v>
+      </c>
+      <c r="X62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="inlineStr"/>
+      <c r="AA62" t="inlineStr"/>
+      <c r="AB62" t="inlineStr"/>
+      <c r="AC62" t="inlineStr"/>
+      <c r="AD62" t="inlineStr"/>
+      <c r="AE62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2448,7 +7035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE2"/>
+  <dimension ref="A1:AE4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2709,6 +7296,214 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>46017.62279666667</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Crash 600 Index</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CRASH → Solo señales de VENTA permitidas</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>16.57</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>50</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>La regresión en el tiempo macro (H1) indica una dirección bajista del 16.57%, sin embargo, no hay coincidencia técnica como RSI alto, MACD cruzando bajista o Heikin Ashi rojo. Como las reglas específi</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>46017.62772520833</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Crash 600 Index</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CRASH → Solo señales de VENTA permitidas</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>222</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Aunque la regresión macro (H1) indica una tendencia alistista, no hay confluencia bajista entre MACD, Heikin Ashi o RSI para dar una señal de venta. En este caso, es mejor esperar a que se produzca un</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2723,7 +7518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE2"/>
+  <dimension ref="A1:AE4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2985,6 +7780,214 @@
       </c>
       <c r="X2" t="n">
         <v>1000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>46017.62301471065</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Crash 900 Index</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CRASH → Solo señales de VENTA permitidas</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>50</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>En este momento, no hay confluencia técnica clara para emitir una señal de venta según las reglas especificadas. La Regresión Macro tiene dirección alciista (1.83%) pero se contrarresta por el indicad</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>46017.62789821759</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Crash 900 Index</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CRASH → Solo señales de VENTA permitidas</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>60.3</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>60</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Con fluencia técnica actual: RSI en sobrecompra (60.3), MACD y Heikin Ashi bajistas, Regresión Macro con dirección alistista pero solo un 1.92%. No se detecta confluencia para ninguna señal de compra </t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2998,7 +8001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE2"/>
+  <dimension ref="A1:AE4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3259,6 +8262,214 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>46017.62319587963</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Jump 75 Index</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>GENÉRICO → Análisis completo</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>50</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>La Regresión Macro muestra dirección bajista y el RSI está en sobrecompra. Sin embargo, el Heikin Ashi indica alcista y el MACD está bajando. Debido a la discrepancia entre estos indicadores, es prude</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>46017.62809283565</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Jump 75 Index</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>GENÉRICO → Análisis completo</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>83.12</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>VENDER</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>7368</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>BLOQUEO: IA y Regresion en direcciones OPUESTAS.</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3273,7 +8484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE2"/>
+  <dimension ref="A1:AE19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3536,6 +8747,1781 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>46017.6233997801</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Volatility 10 Index</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>VOLATILITY → Permite COMPRA/VENTA según tendencia</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>79.79000000000001</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>64.7</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>7979</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>EJECUCION: Alta confianza IA (7979%) alineada con Macro.</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>5706.93</v>
+      </c>
+      <c r="W3" t="n">
+        <v>500</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>46017.62826092593</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Volatility 10 Index</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>VOLATILITY → Permite COMPRA/VENTA según tendencia</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>79.76000000000001</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>7976</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>La regresión lineal en el macro tiempo (H1) tiene un 79.76% de confianza en la dirección alzista, y el MACD también está confirmando esta tendencia. Además, las medias exponenciales (EMA Strategy) tam</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>EJECUCION: Alta confianza IA (7976%) alineada con Macro.</t>
+        </is>
+      </c>
+      <c r="U4" s="6" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>5706.87</v>
+      </c>
+      <c r="W4" t="n">
+        <v>500</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>46017.64341837963</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Volatility 10 Index</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>VOLATILITY → Permite COMPRA/VENTA según tendencia</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>79.77</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>50</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>La regresión lineal en H1 tiene una alta confianza (79.77%) indicando tendencia al ciste, sin embargo, el panel técnico en M5 es neutro y la dirección de MACD y Heikin Ashi están en bajada. Además, la</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>46017.64365708333</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Volatility 10 Index</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>VOLATILITY → Permite COMPRA/VENTA según tendencia</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>79.77</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>544</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>La regresión lineal muestra un estado alistico (79.77%), pero la mayoría de los indicadores técnicos no están confirmando esta tendencia. El RSI y el MACD están en neutral, Heikin Ashi bajista, EMA St</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>46017.64395616898</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Volatility 10 Index</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>VOLATILITY → Permite COMPRA/VENTA según tendencia</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>79.76000000000001</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>543</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Aunque la regresión lineal (H1) tiene una alta confianza alistica, se observa una tendencia neutral en el panel técnico (M5). Además, el RSI se encuentra en el nivel de sobrecompra pero no hay confirm</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>46017.64413917824</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Volatility 10 Index</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>VOLATILITY → Permite COMPRA/VENTA según tendencia</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>79.76000000000001</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>56</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>50</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Regresión Macro en H1 es alcista pero Panel Técnico en M5 es neutral. RSI y MACD no actúan como gatillos de entrada, además, el volumen no se está considerando en este contexto.</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>46017.64456708333</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Volatility 10 Index</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>VOLATILITY → Permite COMPRA/VENTA según tendencia</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>79.76000000000001</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>543</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>46017.64473666667</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Volatility 10 Index</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>VOLATILITY → Permite COMPRA/VENTA según tendencia</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>79.76000000000001</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>508</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>La regresión lineal tiene dirección alistica, pero hay discrepancias en los indicadores MACD y Estocastico que han bajado, Heikin Ashi que es alistica, EMA Strategy que recomienda compra y Micro sopor</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>46017.64510269676</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Volatility 10 Index</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>VOLATILITY → Permite COMPRA/VENTA según tendencia</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>79.76000000000001</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>5432</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">La regresión lineal macro en H1 muestra una tendencia al alza (79.76%), sin embargo, el panel técnico en M5 indica neutralidad (22.2%) y la MACD está bajando. Además, el RSI se encuentra dentro de la </t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>46017.64528837963</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Volatility 10 Index</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>VOLATILITY → Permite COMPRA/VENTA según tendencia</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>79.76000000000001</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>573</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Aunque la regresión lineal está indicando alistamiento, hay una baja confianza en las tendencias técnicas como MACD, Heikin Ashi y Estocastico que no han confirmado esta dirección. Además, el RSI se e</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>46017.64568946759</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Volatility 10 Index</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>VOLATILITY → Permite COMPRA/VENTA según tendencia</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>79.76000000000001</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>495</v>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>La Regresión Macro en H1 tiene un 79.76% de dirección alista, sin embargo el Panel Técnico en M5 muestra una dirección neutra y MACD esta bajando, Heikin Ashi está alista pero no es suficiente para co</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>46017.64586135417</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Volatility 10 Index</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>VOLATILITY → Permite COMPRA/VENTA según tendencia</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>79.76000000000001</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>542</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>46017.64614451389</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Volatility 10 Index</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>VOLATILITY → Permite COMPRA/VENTA según tendencia</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>79.76000000000001</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>556</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>La regresión lineal tiene una tendencia alista pero el panel técnico tiene dirección bajista, la señal debe esperarse para confirmar la tendencia.</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>46017.64662210648</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Volatility 10 Index</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>VOLATILITY → Permite COMPRA/VENTA según tendencia</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>79.76000000000001</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>50</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>La regresión lineal se encuentra alistada, sin embargo, el MACD y el Estocastico apuntan a una venta. Es preciso esperar a que se confirme la tendencia antes de emitir una señal decisiva.</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>46017.64714653936</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Volatility 10 Index</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>VOLATILITY → Permite COMPRA/VENTA según tendencia</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>79.76000000000001</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>50</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>46017.64764547454</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Volatility 10 Index</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>VOLATILITY → Permite COMPRA/VENTA según tendencia</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>79.76000000000001</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>569</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>La regresión lineal tiene una dirección alistista, pero no hay confirme de ello por el MACD o Heikin Ashi. Además, la RSI se encuentra en la zona de sobrecompra. Se recomienda esperar a que se corrobo</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>46017.64814373328</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Volatility 10 Index</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>VOLATILITY → Permite COMPRA/VENTA según tendencia</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>79.76000000000001</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>50</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">La Regresión Macro tiene dirección alcista pero el MACD y RSI no están confirmando esa dirección. Heikin Ashi también está mostrando alcista. Sin embargo, la mayoría de los indicadores no son a favor </t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3548,7 +10534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE2"/>
+  <dimension ref="A1:AE3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3809,6 +10795,110 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>46017.62361434028</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Volatility 100 Index</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>VOLATILITY → Permite COMPRA/VENTA según tendencia</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>72.73</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>VENDER</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>7273</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>La regresión lineal en H1 indica una tendencia descendente con un 72.73% de confianza, confirmada por la dirección alta del MACD y Heikin Ashi. Además, el RSI está dentro del rango neutral (54.6), y h</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>BLOQUEO: IA y Regresion en direcciones OPUESTAS.</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3823,7 +10913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE2"/>
+  <dimension ref="A1:AE3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4084,6 +11174,110 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>46017.62389135417</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Volatility 25 Index</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>VOLATILITY → Permite COMPRA/VENTA según tendencia</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>41.58</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>VENDER</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>667</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>La regresión lineal en H1 presenta una tendencia bajista del 41.58%, sin embargo, el panel técnico en M5 es neutral. La RSI se encuentra en una zona de sobrecompra y la MACD, Heikin Ashi y EMA Strateg</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4098,7 +11292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE2"/>
+  <dimension ref="A1:AE3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4359,6 +11553,110 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>46017.6241199537</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Volatility 50 Index</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>VOLATILITY → Permite COMPRA/VENTA según tendencia</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>426</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>La Regresión Macro presenta una dirección bajista en H1 (31.5%), mientras que el panel técnico es neutral en M5 (11.1%). El RSI se encuentra en la zona de sobrecompra, y aunque el MACD y Heikin Ashi a</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4373,7 +11671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE2"/>
+  <dimension ref="A1:AE3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4635,6 +11933,110 @@
       </c>
       <c r="X2" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>46017.62430165509</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Volatility 75 Index</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>VOLATILITY → Permite COMPRA/VENTA según tendencia</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>72.55</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>7255</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>EJECUCION: Alta confianza IA (7255%) alineada con Macro.</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>43635.81</v>
+      </c>
+      <c r="W3" t="n">
+        <v>500</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1000</v>
       </c>
     </row>
   </sheetData>
@@ -4648,7 +12050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE2"/>
+  <dimension ref="A1:AE3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4810,7 +12212,7 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46010.68734708648</v>
+        <v>46010.68734708333</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -4911,13 +12313,110 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>46017.62450384259</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>XAUUSD → Permite COMPRA/VENTA (requiere alta confirmación)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>73.23999999999999</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>31</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>444</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>La regresión tiene dirección alistica, pero el RSI y el MACD indican una sobrecompra y bajista respectivamente. Además, las demás indicadores no confirman la tendencia. Es necesaria más confluencia pa</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4930,7 +12429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE2"/>
+  <dimension ref="A1:AE4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5191,6 +12690,214 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>46017.62105354167</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Boom 1000 Index</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>BOOM → Solo señales de COMPRA permitidas</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>50.17</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>333</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>La regresión Macro en H1 está apuntando al alcista, pero el MACD, Heikin Ashi y EMA Strategy están indicando una tendencia neutral o baja. La regla de confluencia no se cumple actualmente.</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>46017.62608244213</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Boom 1000 Index</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>BOOM → Solo señales de COMPRA permitidas</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>64.34</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>333</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>La Regresión Macro en H1 indica un estado alcista pero solo con un 33.3% de confianza, no se ha encontrado suficiente confluencia técnica (RSI bajo, MACD cruzando alcista, Heikin Ashi verde) para emit</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5205,7 +12912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE2"/>
+  <dimension ref="A1:AE4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5466,6 +13173,214 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>46017.62122267361</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Boom 500 Index</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>BOOM → Solo señales de COMPRA permitidas</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>628</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>La regresión tiene un R2 de 75.8% en sentido alcista, pero el MACD está en bajada y la EMA Strategy muestra venta. Heikin Ashi es el único indicador que confirma una tendencia alcista.</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>46017.62629886574</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Boom 500 Index</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>BOOM → Solo señales de COMPRA permitidas</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>44.35</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>333</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>No se ha encontrado confluencia alcista en el momento actual, RSI y MACD están bajistas y Heikin Ashi también está bajista. Además, EMA Strategy indica venta. Sin embargo, la regresión macro de H1 tie</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5480,7 +13395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE2"/>
+  <dimension ref="A1:AE4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5741,6 +13656,214 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>46017.62141868056</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Boom 300 Index</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>BOOM → Solo señales de COMPRA permitidas</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>62.62</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>VENDER</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>333</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Regresión Macro (H1) presenta dirección bajista, mientras que panel técnico (M5) es neutro. Además, el RSI está sobrecompra y MACD está bajista, sin embargo, Heikin Ashi indica alcista. Por lo tanto, </t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>46017.62647211806</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Boom 300 Index</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>BOOM → Solo señales de COMPRA permitidas</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>222</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Se ha identificado una tendencia neutral en el panel técnico M5 y baja dirección en la regresión Macro H1, lo que indica falta de confluencia alcista para emitir una señal de compra. Se recomienda esp</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5755,7 +13878,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE2"/>
+  <dimension ref="A1:AE4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6016,6 +14139,214 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>46017.62167224537</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Boom 600 Index</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>BOOM → Solo señales de COMPRA permitidas</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>23.28</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>45</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>La regresión Macro en H1 tiene una dirección bajista del 23.28% y la Panel Tecnico en M5 es neutra con un 11.1%. Aunque Heikin Ashi está verde indicando alcista, RSI está sobrecompra con un valor de 4</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>46017.62668939814</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Boom 600 Index</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>BOOM → Solo señales de COMPRA permitidas</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>39.55</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>75</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El MACD está en alcista y el RSI se encuentra por debajo de 65, lo que indica una sobrecompra posible. Sin embargo, el Heikin Ashi está en baja, lo que es un signo ligeramente contrario. Sin embargo, </t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>BLOQUEO: IA y Regresion en direcciones OPUESTAS.</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6030,7 +14361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE2"/>
+  <dimension ref="A1:AE4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6291,6 +14622,214 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>46017.62190553241</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Boom 900 Index</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>BOOM → Solo señales de COMPRA permitidas</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>333</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>La Regresión Macro (H1) tiene un valor del 6.49% en dirección alcista y el Panel Técnico (M5) indica un estado neutral de 33.3%, sin embargo, no hay confluencia alcista confirmada en RSI, MACD o Heiki</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>46017.62689240741</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Boom 900 Index</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>BOOM → Solo señales de COMPRA permitidas</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>18.64</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>40</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>La regresión macro en H1 está indicando una dirección alista, pero los gatillos MACD y Heikin Ashi no confirmaron esa tendencia. Además, el RSI se encuentra sobrecompra con un valor de 21.5. Por lo ta</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6305,7 +14844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE2"/>
+  <dimension ref="A1:AE4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6566,6 +15105,214 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>46017.62214969908</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Crash 1000 Index</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CRASH → Solo señales de VENTA permitidas</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>75</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>En el Crash 1000 Index, se observa una sobrecompra según el RSI (60.2), lo que sugiere que la venta puede ser una buena opción. Además, el MACD está en alzista y Heikin Ashi es bajista, lo que confirm</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>BLOQUEO: IA y Regresion en direcciones OPUESTAS.</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>46017.62711271991</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Crash 1000 Index</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CRASH → Solo señales de VENTA permitidas</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>15.87</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>60</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Aunque la Regresión Macro (H1) muestra un valor alto (15.87%) en sentido alistista, el RSI se encuentra sobre el 51.2% lo que indica sobrecompra. Además, el MACD está en alistista y Heikin Ashi es baj</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6580,7 +15327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE2"/>
+  <dimension ref="A1:AE4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6841,6 +15588,214 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>46017.62237793981</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Crash 500 Index</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CRASH → Solo señales de VENTA permitidas</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>15.39</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>63.7</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>50</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>A pesar de que la regresión tiene una dirección alistista, no se observa coincidencia bajista entre los gatillos MACD y Heikin Ashi. Además, el RSI está sobrecompra (63.7) y las estrategias EMA y Stoc</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>46017.62729516203</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Crash 500 Index</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CRASH → Solo señales de VENTA permitidas</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>71.52</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>50</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aunque la regresión macro (H1) muestra una alciista del 71.52%, no se confirma con el MACD, Heikin Ashi y RSI, los cuales están indicando una sobreventa, por lo tanto es mejor esperar a encontrar una </t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6855,7 +15810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE2"/>
+  <dimension ref="A1:AE4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7116,6 +16071,214 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>46017.62257717593</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Crash 300 Index</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CRASH → Solo señales de VENTA permitidas</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>90.61</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>667</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>La Regresión Macro en H1 está mostrando una tendencia alista con un R2 de 90.61%, pero el MACD y Heikin Ashi están bajistas. Además, el RSI no muestra un sobrecompra ni sobreventa, por lo que es prude</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Sin confluencia clara.</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>46017.62754586805</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Crash 300 Index</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CRASH → Solo señales de VENTA permitidas</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ALCISTA</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>91.79000000000001</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>BAJISTA</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>9179</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>La regresión Macro en H1 es alcista (91.79%) indicando una tendencia de subida. Sin embargo, el RSI está sobrecompra (72.2), MACD también alcista y Heikin Ashi bajista, lo que indica una posible tende</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>BLOQUEO: IA y Regresion en direcciones OPUESTAS.</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>ESPERAR</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
         <v>0</v>
       </c>
     </row>
